--- a/SGC-CKN/Excel/g94x8_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
+++ b/SGC-CKN/Excel/g94x8_Cọc_khoan_nhồi_-_Trụ_HN_P479_C9_D2000_04-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="104">
   <si>
     <t>Dự án</t>
   </si>
@@ -29,7 +29,7 @@
     <t>Tên bộ phận</t>
   </si>
   <si>
-    <t>Cọc khoan nhồi - Trụ HN P479</t>
+    <t>Cọc khoan nhồi - Trụ HN&amp;&amp;&amp;&amp;&amp;P479</t>
   </si>
   <si>
     <t>Số hiệu cọc</t>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>(27)</t>
-  </si>
-  <si>
-    <t>ẢNH BIÊN BẢN GỐC</t>
   </si>
   <si>
     <t>STT</t>
@@ -363,7 +360,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -427,12 +424,6 @@
     <font>
       <color rgb="FF365314"/>
       <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -515,7 +506,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -570,21 +561,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF1A3A6B"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF1A3A6B"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF1A3A6B"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF1A3A6B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
@@ -602,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -679,13 +655,10 @@
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -703,50 +676,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="8096250" cy="10477500"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1071,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2199,83 +2128,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
-    </row>
-    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B1:K1"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="B3:K3"/>
@@ -2284,11 +2138,9 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B8:K8"/>
-    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2307,31 +2159,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2509,31 +2361,31 @@
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="B8" s="28" t="s">
+      <c r="A8" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
         <v>27</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
         <v>-6.72</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
         <v>-63</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <v>28.03</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <v>56.28</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <v>2.01</v>
       </c>
     </row>
